--- a/diseases/d142/2010-2014.xlsx
+++ b/diseases/d142/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>149</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>2.778114165762614</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>613</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>11.42942270880861</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>1128</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>21.03162938912905</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>484</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>9.0242097733497</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>114</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>2.125537012731128</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>16</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.2983209842429653</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>9</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.167805553636668</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>11</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.2050956766670386</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>19</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.3542561687885213</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>27</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.5034166609100039</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>26</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.4847715993948186</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>53</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.9836234125385261</v>
       </c>
@@ -7985,9 +7946,6 @@
       <c r="O42" t="n">
         <v>145</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>2.691045185246911</v>
       </c>
@@ -8529,9 +8487,6 @@
       <c r="O45" t="n">
         <v>323</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>5.994535136791395</v>
       </c>
@@ -9073,9 +9028,6 @@
       <c r="O48" t="n">
         <v>324</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>6.013094069103442</v>
       </c>
@@ -9617,9 +9569,6 @@
       <c r="O51" t="n">
         <v>131</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>2.431220132878244</v>
       </c>
@@ -10161,9 +10110,6 @@
       <c r="O54" t="n">
         <v>44</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.8165930217300971</v>
       </c>
@@ -10705,9 +10651,6 @@
       <c r="O57" t="n">
         <v>12</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.2227071877445719</v>
       </c>
@@ -11249,9 +11192,6 @@
       <c r="O60" t="n">
         <v>6</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.111353593872286</v>
       </c>
@@ -11793,9 +11733,6 @@
       <c r="O63" t="n">
         <v>13</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.2412661200566196</v>
       </c>
@@ -12337,9 +12274,6 @@
       <c r="O66" t="n">
         <v>24</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.4454143754891438</v>
       </c>
@@ -12881,9 +12815,6 @@
       <c r="O69" t="n">
         <v>90</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>1.670303908084289</v>
       </c>
@@ -13425,9 +13356,6 @@
       <c r="O72" t="n">
         <v>357</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>6.625538835401015</v>
       </c>
@@ -13969,9 +13897,6 @@
       <c r="O75" t="n">
         <v>697</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>12.87409806276225</v>
       </c>
@@ -14513,9 +14438,6 @@
       <c r="O78" t="n">
         <v>942</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>17.39942665010335</v>
       </c>
@@ -15057,9 +14979,6 @@
       <c r="O81" t="n">
         <v>434</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>8.016296354718527</v>
       </c>
@@ -15601,9 +15520,6 @@
       <c r="O84" t="n">
         <v>110</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>2.031780182071516</v>
       </c>
@@ -16145,9 +16061,6 @@
       <c r="O87" t="n">
         <v>33</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.6095340546214548</v>
       </c>
@@ -16689,9 +16602,6 @@
       <c r="O90" t="n">
         <v>12</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.2216487471350745</v>
       </c>
@@ -17233,9 +17143,6 @@
       <c r="O93" t="n">
         <v>7</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.1292951024954601</v>
       </c>
@@ -17777,9 +17684,6 @@
       <c r="O96" t="n">
         <v>6</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.1108243735675373</v>
       </c>
@@ -18321,9 +18225,6 @@
       <c r="O99" t="n">
         <v>4</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.0738829157116915</v>
       </c>
@@ -19309,9 +19210,6 @@
       <c r="O105" t="n">
         <v>8</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.147765831423383</v>
       </c>
@@ -20445,9 +20343,6 @@
       <c r="O112" t="n">
         <v>25</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.4617682231980719</v>
       </c>
@@ -21581,9 +21476,6 @@
       <c r="O119" t="n">
         <v>67</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>1.237538838170833</v>
       </c>
@@ -22865,9 +22757,6 @@
       <c r="O127" t="n">
         <v>197</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>3.621954042367302</v>
       </c>
@@ -24001,9 +23890,6 @@
       <c r="O134" t="n">
         <v>387</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>7.11520921013272</v>
       </c>
@@ -25137,9 +25023,6 @@
       <c r="O141" t="n">
         <v>565</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>10.38783773572348</v>
       </c>
@@ -26421,9 +26304,6 @@
       <c r="O149" t="n">
         <v>471</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>8.659595705355326</v>
       </c>
@@ -27557,9 +27437,6 @@
       <c r="O156" t="n">
         <v>215</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>3.952894005629288</v>
       </c>
@@ -28693,9 +28570,6 @@
       <c r="O163" t="n">
         <v>49</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.9008921222131868</v>
       </c>
@@ -29977,9 +29851,6 @@
       <c r="O171" t="n">
         <v>17</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.3125544097474321</v>
       </c>
@@ -31113,9 +30984,6 @@
       <c r="O178" t="n">
         <v>4</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.07354221405821933</v>
       </c>
@@ -32397,9 +32265,6 @@
       <c r="O186" t="n">
         <v>10</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.1838555351455483</v>
       </c>
@@ -33533,9 +33398,6 @@
       <c r="O193" t="n">
         <v>15</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.2757833027183225</v>
       </c>
@@ -34669,9 +34531,6 @@
       <c r="O200" t="n">
         <v>12</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.220626642174658</v>
       </c>
@@ -35953,9 +35812,6 @@
       <c r="O208" t="n">
         <v>49</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.9008921222131868</v>
       </c>
@@ -37089,9 +36945,6 @@
       <c r="O215" t="n">
         <v>125</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>2.288671406108445</v>
       </c>
@@ -38225,9 +38078,6 @@
       <c r="O222" t="n">
         <v>494</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>9.044829396940576</v>
       </c>
@@ -39361,9 +39211,6 @@
       <c r="O229" t="n">
         <v>973</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>17.81501822514814</v>
       </c>
@@ -40645,9 +40492,6 @@
       <c r="O237" t="n">
         <v>786</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>14.39116580160991</v>
       </c>
@@ -41781,9 +41625,6 @@
       <c r="O244" t="n">
         <v>290</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>5.309717662171594</v>
       </c>
@@ -43065,9 +42906,6 @@
       <c r="O252" t="n">
         <v>57</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>1.043634161185451</v>
       </c>
@@ -44201,9 +44039,6 @@
       <c r="O259" t="n">
         <v>23</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.421115538723954</v>
       </c>
@@ -45337,9 +45172,6 @@
       <c r="O266" t="n">
         <v>10</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.1830937124886756</v>
       </c>
@@ -46621,9 +46453,6 @@
       <c r="O274" t="n">
         <v>11</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.2014030837375432</v>
       </c>
@@ -47757,9 +47586,6 @@
       <c r="O281" t="n">
         <v>17</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.3112593112307486</v>
       </c>
@@ -48893,9 +48719,6 @@
       <c r="O288" t="n">
         <v>28</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.5126623949682918</v>
       </c>
@@ -50176,9 +49999,6 @@
       </c>
       <c r="O296" t="n">
         <v>54</v>
-      </c>
-      <c r="Q296" t="n">
-        <v>0</v>
       </c>
       <c r="R296" t="n">
         <v>0.9887060474388486</v>
